--- a/artfynd/A 26040-2026 artfynd.xlsx
+++ b/artfynd/A 26040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925265</v>
       </c>
       <c r="B2" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>134232412</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>134232410</v>
       </c>
       <c r="B4" t="n">
-        <v>80485</v>
+        <v>80492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>134232411</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>92539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26040-2026 artfynd.xlsx
+++ b/artfynd/A 26040-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133925265</v>
+        <v>134232411</v>
       </c>
       <c r="B2" t="n">
-        <v>80481</v>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772452</v>
+        <v>772774</v>
       </c>
       <c r="R2" t="n">
-        <v>7325120</v>
+        <v>7324673</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232412</v>
+        <v>133925265</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772837</v>
+        <v>772452</v>
       </c>
       <c r="R3" t="n">
-        <v>7325140</v>
+        <v>7325120</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,9 +853,19 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232410</v>
+        <v>134232412</v>
       </c>
       <c r="B4" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772776</v>
+        <v>772837</v>
       </c>
       <c r="R4" t="n">
-        <v>7324676</v>
+        <v>7325140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1003,32 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134232411</v>
+        <v>134232410</v>
       </c>
       <c r="B5" t="n">
-        <v>92539</v>
+        <v>80499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772774</v>
+        <v>772776</v>
       </c>
       <c r="R5" t="n">
-        <v>7324673</v>
+        <v>7324676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26040-2026 artfynd.xlsx
+++ b/artfynd/A 26040-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232411</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925265</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,8 +1126,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232410</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>